--- a/output/第10期計画_保険料と施策評価の他団体比較.xlsx
+++ b/output/第10期計画_保険料と施策評価の他団体比較.xlsx
@@ -4831,10 +4831,10 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1">
+    <row r="28" ht="72" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>注1）出典は見える化W144・W145及びW135〜W143（令和5年調査）。注2）本シートの最も重要な所見は、長期の実績が良好である一方、直近の変化率が全国と逆方向に動いていることである。自然体推計は過去の傾向を将来に延長する方法であるため、どの期間の傾向を採るかによって認定者数の推計が大きく変わる。注3）良好な長期実績が施設・居住系への入所によるものである場合、介護老人福祉施設の定員が234人から160人へ減少している状況では、同じ実績が続く保証はない。これは推計の下方リスクである。注4）Ⅳ-5（性・年齢調整済み要介護2以上認定率）は代表KPI H01のデータ源である。水準・変化とも全国より悪い方向にあることを、目標設定の出発点とする。</t>
+          <t>注1）出典は見える化W144・W145及びW135〜W143（令和5年調査）。注2）本シートの最も重要な所見は、長期の実績が良好である一方、直近の変化率が全国と逆方向に動いていることである。自然体推計は過去の傾向を将来に延長する方法であるため、どの期間の傾向を採るかによって認定者数の推計が大きく変わる。注3）良好な長期実績が施設・居住系への入所によるものである場合、介護老人福祉施設の定員が234人から160人へ減少している状況では、同じ実績が続く保証はない。これは推計の下方リスクである。注4）Ⅳ-5（性・年齢調整済み要介護2以上認定率）は代表KPI H01のデータ源である。水準・変化とも全国より悪い方向にあることを、目標設定の出発点とする。注5）【令和8年7月29日追記】見える化B5aによる要介護2以上の調整済み認定率は、平成30年8.4％から令和7年7.3％へ1.1ポイント低下している。W144（9.25％・変化率＋1.76）とは基準人口・調整方法・時点・単位が異なるため直接比較できない。両者を同じものとして並べてはならない（認定率の年齢調整分析 05シート）。また従来「軽度は改善・中重度は悪化」と説明していたが、B6a・B6bにより逆であることが判明したため撤回した。</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>②認定者数　重度化の速度</t>
+          <t>②認定者数　重度化の速度【令和8年7月29日改訂】</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>ウを基本とし、イを需要上振れシナリオとする。長期の良好な実績が施設入所によるものである可能性があり、施設定員が234人から160人へ減少している状況では同じ実績が続く保証がないため、アは採らない。</t>
+          <t>【改訂】見える化B6a・B6bの調整済み認定率により、重度（要介護3〜5）は平成30年5.4％から令和7年4.7％へ低下が続き、軽度（要支援1〜要介護2）は令和5年11.7％を底に令和7年12.0％へ上昇に転じていることが確認された（認定率の年齢調整分析 04シート）。重度化が加速しているという前提の根拠は薄い。重度はウ（全国並みに収束）を基本とし、軽度は直近の上昇を反映して別に見込む。認定者数の推計を軽度と重度に分けて行うことを提案する。施設定員が234人から160人へ減少している状況では長期の良好な実績が続く保証がないため、アは採らない。</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">

--- a/output/第10期計画_保険料と施策評価の他団体比較.xlsx
+++ b/output/第10期計画_保険料と施策評価の他団体比較.xlsx
@@ -2723,7 +2723,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>見える化システムの地域差指数（性・年齢調整後、全国＝1.00）により、給付水準の高さがどの要素に由来するかを分解する。将来推計では、どの要素を将来に延長するかによって結果が変わるため、現在の水準の要因を特定しておく必要がある。</t>
+          <t>見える化システムの地域差指数（性・年齢調整後、全国＝1.00）により、給付水準の高さがどの要素の差によるものかを分解する。将来推計では、どの要素を将来に延長するかによって結果が変わるため、現在の水準の要因を特定しておく必要がある。</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>全国比1.08。給付水準の高さはここに集約される（妥当性検証 所見1）</t>
+          <t>全国比1.08。給付水準の高さの大半はこの差による（妥当性検証 所見1）</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_保険料と施策評価の他団体比較.xlsx
+++ b/output/第10期計画_保険料と施策評価の他団体比較.xlsx
@@ -2673,7 +2673,7 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>注1）必要保険料月額は見える化P4「必要保険料額（合計）」による。令和6年度は令和8年1月時点の実績を年度換算した概算値である。注2）第7期・第8期の必要額の平均は、上表の年度別の値の単純平均である。注3）基金残高及び取崩実績の資料が未受領であるため、剰余が基金に積み立てられているかどうかは確認できていない（確認事項No.16）。第10期の取崩額を決めるには、令和8年度末の基金残高見込が必要である。注4）予定収納率99.0％の妥当性は、第7期から第9期の収納率実績により検証する。注5）第7期の保険料基準額について、見える化システムの値は6,077円であるが、計画素案の第9稿までは5,900円としていた。累計＋159円／月という剰余の値は6,077円を前提としたときにのみ整合するため（(6,077－6,024)×3＝159）、本表は6,077円によっている。条例による第7期の基準額の確認を要する（08シート No.10）。</t>
+          <t>注1）必要保険料月額は見える化P4「必要保険料額（合計）」による。令和6年度は令和8年1月時点の実績を年度換算した概算値である。注2）第7期・第8期の必要額の平均は、上表の年度別の値の単純平均である。注3）基金残高及び取崩実績の資料が未受領であるため、剰余が基金に積み立てられているかどうかは確認できていない（確認事項No.16）。第10期の取崩額を決めるには、令和8年度末の基金残高見込が必要である。注4）予定収納率99.0％の妥当性は、第7期から第9期の収納率実績により検証する。注5）第7期の保険料基準額6,077円は、見える化C1（介護保険事業計画報告値）により平成30年度〜令和2年度の第1号保険料月額として確認した（令和8年7月30日受領。地域差の分析11シート）。計画素案の第9稿までは5,900円としていたが、6,077円に確定した。注6）期別の保険料基準額は、第5期5,100円、第6期5,776円、第7期6,077円、第8期6,300円、第9期6,400円である（見える化C1）。第5期から第9期で1,300円（25.5％）上昇している。</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>第7期の保険料基準額</t>
+          <t>第7期の保険料基準額（解消）</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>見える化システムの値は6,077円であるが、計画素案の第9稿までは5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときに整合する。条例による第7期の基準額の確認を要する。</t>
+          <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。期別の基準額は第5期5,100円・第6期5,776円・第7期6,077円・第8期6,300円・第9期6,400円である。条例による確認は不要となった。</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>―（解消）</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>解消</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_保険料と施策評価の他団体比較.xlsx
+++ b/output/第10期計画_保険料と施策評価の他団体比較.xlsx
@@ -2673,7 +2673,7 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>注1）必要保険料月額は見える化P4「必要保険料額（合計）」による。令和6年度は令和8年1月時点の実績を年度換算した概算値である。注2）第7期・第8期の必要額の平均は、上表の年度別の値の単純平均である。注3）基金残高及び取崩実績の資料が未受領であるため、剰余が基金に積み立てられているかどうかは確認できていない（確認事項No.16）。第10期の取崩額を決めるには、令和8年度末の基金残高見込が必要である。注4）予定収納率99.0％の妥当性は、第7期から第9期の収納率実績により検証する。注5）第7期の保険料基準額6,077円は、見える化C1（介護保険事業計画報告値）により平成30年度〜令和2年度の第1号保険料月額として確認した（令和8年7月30日受領。地域差の分析11シート）。計画素案の第9稿までは5,900円としていたが、6,077円に確定した。注6）期別の保険料基準額は、第5期5,100円、第6期5,776円、第7期6,077円、第8期6,300円、第9期6,400円である（見える化C1）。第5期から第9期で1,300円（25.5％）上昇している。</t>
+          <t>注1）必要保険料月額は見える化P4「必要保険料額（合計）」による。令和6年度は令和8年1月時点の実績を年度換算した概算値である。注2）第7期・第8期の必要額の平均は、上表の年度別の値の単純平均である。注3）基金残高及び取崩実績の資料が未受領であるため、剰余が基金に積み立てられているかどうかは確認できていない（確認事項No.16）。第10期の取崩額を決めるには、令和8年度末の基金残高見込が必要である。注4）予定収納率99.0％の妥当性は、第7期から第9期の収納率実績により検証する。注5）第7期の保険料基準額6,077円は、見える化C1（介護保険事業計画報告値）により平成30年度〜令和2年度の第1号保険料月額として確認した（令和8年7月30日受領。地域差の分析11シート）。計画素案では当初5,900円としていたが、6,077円に確定した。注6）期別の保険料基準額は、第5期5,100円、第6期5,776円、第7期6,077円、第8期6,300円、第9期6,400円である（見える化C1）。第5期から第9期で1,300円（25.5％）上昇している。</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>全国の123.5％。全国トップ級</t>
+          <t>全国の123.5％。令和6年度分の指標では全国平均を上回る</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_保険料と施策評価の他団体比較.xlsx
+++ b/output/第10期計画_保険料と施策評価の他団体比較.xlsx
@@ -3742,7 +3742,7 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>【解釈】成果（アウトカム）は全国を上回る一方、活動（アウトプット）の記録・報告が全国の23.2〜55.6％にとどまる。結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない</t>
+          <t>【解釈】成果（アウトカム）は全国を上回る一方、活動（アウトプット）の得点が全国の23.2〜55.6％にとどまる。この差が、未実施・要件未充足・記録又は報告の不備のいずれによるかは評価調書（資料No.5）で確認する。現時点では未確認</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
